--- a/Proyecto 1 - Etapa 1/prediccionesRandomForest.xlsx
+++ b/Proyecto 1 - Etapa 1/prediccionesRandomForest.xlsx
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -2327,7 +2327,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4102,7 +4102,7 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -5977,7 +5977,7 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223">
@@ -9554,7 +9554,7 @@
         </is>
       </c>
       <c r="E365" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="366">
@@ -11937,7 +11937,7 @@
         </is>
       </c>
       <c r="E460" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="461">
@@ -12012,7 +12012,7 @@
         </is>
       </c>
       <c r="E463" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="464">
@@ -12612,7 +12612,7 @@
         </is>
       </c>
       <c r="E487" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="488">
@@ -13862,7 +13862,7 @@
         </is>
       </c>
       <c r="E537" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="538">
@@ -14689,7 +14689,7 @@
         </is>
       </c>
       <c r="E570" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="571">
@@ -16139,7 +16139,7 @@
         </is>
       </c>
       <c r="E628" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="629">
@@ -22039,7 +22039,7 @@
         </is>
       </c>
       <c r="E864" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="865">
